--- a/Results/Study 1/GoogLeNet (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 1/GoogLeNet (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="C2">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C3">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Study 1/GoogLeNet (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 1/GoogLeNet (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>495</v>
+        <v>528</v>
       </c>
       <c r="C2">
-        <v>145</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="C3">
-        <v>422</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C3">
-        <v>85</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
